--- a/DataTables/Datas/#InputData-按键输入表.xlsx
+++ b/DataTables/Datas/#InputData-按键输入表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="19200" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>UnitControl</t>
   </si>
   <si>
-    <t>player</t>
+    <t>Player</t>
   </si>
   <si>
     <t>&lt;Mouse&gt;/leftButton</t>
